--- a/test/datos_prueba.xlsx
+++ b/test/datos_prueba.xlsx
@@ -1,41 +1,254 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico_\Desktop\Trabajo\ProyectosRandom\Multicopy\test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C0634B-2E2F-40F0-AAE8-B01594E0D1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Personas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+  <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Fecha Nacimiento</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Acepta Términos</t>
+  </si>
+  <si>
+    <t>Tipo Contrato</t>
+  </si>
+  <si>
+    <t>12.345.678-9</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>juan.perez@empresa.cl</t>
+  </si>
+  <si>
+    <t>912345678</t>
+  </si>
+  <si>
+    <t>20/08/1990</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Ingeniero de Software Senior con experiencia en arquitectura cloud.</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Indefinido</t>
+  </si>
+  <si>
+    <t>18.765.432-1</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>Soto</t>
+  </si>
+  <si>
+    <t>maria.soto@empresa.cl</t>
+  </si>
+  <si>
+    <t>987654321</t>
+  </si>
+  <si>
+    <t>15/03/1995</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Diseñadora UX/UI especialista en Design Systems y Figma.</t>
+  </si>
+  <si>
+    <t>Plazo Fijo</t>
+  </si>
+  <si>
+    <t>15.987.654-3</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>González</t>
+  </si>
+  <si>
+    <t>carlos.gonzalez@consultora.cl</t>
+  </si>
+  <si>
+    <t>955512345</t>
+  </si>
+  <si>
+    <t>10/11/1988</t>
+  </si>
+  <si>
+    <t>Consultor DevOps y especialista en Docker y Kubernetes.</t>
+  </si>
+  <si>
+    <t>Honorarios</t>
+  </si>
+  <si>
+    <t>19.456.789-0</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>Rojas</t>
+  </si>
+  <si>
+    <t>camila.rojas@techcorp.com</t>
+  </si>
+  <si>
+    <t>977788990</t>
+  </si>
+  <si>
+    <t>05/07/1997</t>
+  </si>
+  <si>
+    <t>Desarrolladora Frontend React y Vue con 4 años de experiencia.</t>
+  </si>
+  <si>
+    <t>11.223.344-5</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>roberto.munoz@innovacion.cl</t>
+  </si>
+  <si>
+    <t>944433221</t>
+  </si>
+  <si>
+    <t>12/01/1982</t>
+  </si>
+  <si>
+    <t>Project Manager certificado PMP con manejo de metodologías ágiles Scrum.</t>
+  </si>
+  <si>
+    <t>17.332.114-K</t>
+  </si>
+  <si>
+    <t>Valentina</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>v.morales@analytics.cl</t>
+  </si>
+  <si>
+    <t>966677889</t>
+  </si>
+  <si>
+    <t>28/09/1993</t>
+  </si>
+  <si>
+    <t>Científica de Datos con dominio en Python, Pandas y Machine Learning.</t>
+  </si>
+  <si>
+    <t>16.889.900-2</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>ignacio.bravo@bravobytes.cl</t>
+  </si>
+  <si>
+    <t>933322110</t>
+  </si>
+  <si>
+    <t>14/04/1991</t>
+  </si>
+  <si>
+    <t>Analista Programador Fullstack y creador de soluciones web a medida.</t>
+  </si>
+  <si>
+    <t>20.112.233-4</t>
+  </si>
+  <si>
+    <t>Francisca</t>
+  </si>
+  <si>
+    <t>Vargas</t>
+  </si>
+  <si>
+    <t>fran.vargas@marketing.com</t>
+  </si>
+  <si>
+    <t>988899001</t>
+  </si>
+  <si>
+    <t>03/12/1999</t>
+  </si>
+  <si>
+    <t>Especialista en Growth Marketing y optimización de conversiones.</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +278,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,300 +617,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>RUT</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Apellido</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Teléfono</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Fecha Nacimiento</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Sexo</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Observaciones</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Acepta Términos</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Tipo Contrato</v>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12.345.678-9</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Juan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pérez</v>
-      </c>
-      <c r="D2" t="str">
-        <v>juan.perez@empresa.cl</v>
-      </c>
-      <c r="E2" t="str">
-        <v>912345678</v>
-      </c>
-      <c r="F2" t="str">
-        <v>20/08/1990</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Masculino</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Ingeniero de Software Senior con experiencia en arquitectura cloud.</v>
-      </c>
-      <c r="I2" t="str">
-        <v>si</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Indefinido</v>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>18.765.432-1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>María</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Soto</v>
-      </c>
-      <c r="D3" t="str">
-        <v>maria.soto@empresa.cl</v>
-      </c>
-      <c r="E3" t="str">
-        <v>987654321</v>
-      </c>
-      <c r="F3" t="str">
-        <v>15/03/1995</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Femenino</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Diseñadora UX/UI especialista en Design Systems y Figma.</v>
-      </c>
-      <c r="I3" t="str">
-        <v>si</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Plazo Fijo</v>
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>15.987.654-3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Carlos</v>
-      </c>
-      <c r="C4" t="str">
-        <v>González</v>
-      </c>
-      <c r="D4" t="str">
-        <v>carlos.gonzalez@consultora.cl</v>
-      </c>
-      <c r="E4" t="str">
-        <v>955512345</v>
-      </c>
-      <c r="F4" t="str">
-        <v>10/11/1988</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Masculino</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Consultor DevOps y especialista en Docker y Kubernetes.</v>
-      </c>
-      <c r="I4" t="str">
-        <v>si</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Honorarios</v>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>19.456.789-0</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Camila</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Rojas</v>
-      </c>
-      <c r="D5" t="str">
-        <v>camila.rojas@techcorp.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>977788990</v>
-      </c>
-      <c r="F5" t="str">
-        <v>05/07/1997</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Femenino</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Desarrolladora Frontend React y Vue con 4 años de experiencia.</v>
-      </c>
-      <c r="I5" t="str">
-        <v>si</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Indefinido</v>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>11.223.344-5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Roberto</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Muñoz</v>
-      </c>
-      <c r="D6" t="str">
-        <v>roberto.munoz@innovacion.cl</v>
-      </c>
-      <c r="E6" t="str">
-        <v>944433221</v>
-      </c>
-      <c r="F6" t="str">
-        <v>12/01/1982</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Masculino</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Project Manager certificado PMP con manejo de metodologías ágiles Scrum.</v>
-      </c>
-      <c r="I6" t="str">
-        <v>si</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Indefinido</v>
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>17.332.114-K</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Valentina</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Morales</v>
-      </c>
-      <c r="D7" t="str">
-        <v>v.morales@analytics.cl</v>
-      </c>
-      <c r="E7" t="str">
-        <v>966677889</v>
-      </c>
-      <c r="F7" t="str">
-        <v>28/09/1993</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Femenino</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Científica de Datos con dominio en Python, Pandas y Machine Learning.</v>
-      </c>
-      <c r="I7" t="str">
-        <v>si</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Plazo Fijo</v>
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>16.889.900-2</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Ignacio</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Bravo</v>
-      </c>
-      <c r="D8" t="str">
-        <v>ignacio.bravo@bravobytes.cl</v>
-      </c>
-      <c r="E8" t="str">
-        <v>933322110</v>
-      </c>
-      <c r="F8" t="str">
-        <v>14/04/1991</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Masculino</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Analista Programador Fullstack y creador de soluciones web a medida.</v>
-      </c>
-      <c r="I8" t="str">
-        <v>si</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Indefinido</v>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>20.112.233-4</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Francisca</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Vargas</v>
-      </c>
-      <c r="D9" t="str">
-        <v>fran.vargas@marketing.com</v>
-      </c>
-      <c r="E9" t="str">
-        <v>988899001</v>
-      </c>
-      <c r="F9" t="str">
-        <v>03/12/1999</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Femenino</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Especialista en Growth Marketing y optimización de conversiones.</v>
-      </c>
-      <c r="I9" t="str">
-        <v>si</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Honorarios</v>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError sqref="A1:J1 A4:J7 B3:I3 A9:F9 H9:J9 A2 C2:J2 A8:F8 H8:J8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>